--- a/human_validation/judge/kor/judge_D001_S005_P002__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D001_S005_P002__claude-sonnet-5_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,103 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 저는 스미스 선생님입니다. 오늘 어떤 일로 찾아오셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 음, 가장 큰 건 제가 항상 이거 하다가 저거 하다가 계속 옮겨 다니는 느낌이 든다는 거예요. 그냥 가만히 앉아서 아무것도 안 하는 게 잘 안 돼요. 직장에서 새로 바뀐 체제 때문에 그걸 감추거나 그냥 넘어가기가 더 힘들어져서, 병원에 와서 누구랑 이야기해봐야겠다고 생각했어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 주의력결핍 과잉행동장애 (부주의 우세형) (D002)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 항상 움직이거나 바빠야 할 것 같은 이 느낌이 어렸을 때부터 있었던 건지, 아니면 성인이 되고 나서 최근에 시작된 건지 말씀해 주시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 아니요, 새로운 게 아니에요. 돌이켜보면 어렸을 때도 있었어요. 초등학교 때 선생님들이 제가 똑똑한데 좀 덤벙댄다고, 순서 안 지키고 말한다거나 과제에 집중하려면 계속 상기시켜줘야 한다고 하셨어요. 그게 지금이랑 연결된다는 걸 최근에야 제대로 깨달은 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 지금 일상생활에서도 신체적으로 안절부절못하거나, 가만히 있지 못하거나, 다른 사람 말을 끊거나 깊이 생각하지 않고 빠르게 결정을 내리는 것처럼 충동적으로 행동하는 걸 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 네, 그런 걸 느껴요. 교육 영상이나 긴 진료처럼 느린 걸 계속 앉아서 봐야 하면, 뭔가 갇힌 것 같은 느낌이 들기 시작해요. 일어나고 싶고, 몸을 좀 펴고 싶고, 자세를 바꾸고 싶고, 아니면 손으로 뭔가라도 하고 싶어져요. 크게 티가 나진 않는데, 분명히 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 안절부절못하는 느낌이 없을 때도, 세부적인 걸 놓치거나, 뭔가를 잊어버리거나, 업무를 정리하거나 집중하는 데 어려움을 겪으시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 네, 그래요. 주로 긴 회의를 할 때나 직장에서 새 업무 절차를 읽으려고 할 때 그래요. 처음엔 괜찮게 시작하는데, 몇 분 지나면 제 눈은 계속 페이지를 훑고 있었는데도, 아니면 앉아서 듣고는 있었는데도 실제로는 무슨 말인지 제대로 받아들이지 못했다는 걸 깨달아요. 그럼 다시 돌아가서 따라잡으려고 해야 해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>진단명: 주의력결핍 과잉행동장애 (복합형) (D001)
 인구통계: 성별 남성 / 나이 57 / 직업상태 customer service representative / 최종학력 고등학교 졸업
@@ -575,161 +663,46 @@
 증상 지속 기간: 1 year and 10 months
 추가 요건: Onset prior to age 12 years
 주호소 증상 코드: S014
-배경 서술: 데니스가 근무하던 콜센터는 그의 업무를 익숙했던 전화 기반 고객 응대에서 실시간 채팅, CRM 문서 작업, 여러 디지털 플랫폼에 걸친 신속한 에스컬레이션 처리를 함께 담당하는 혼합형 직무로 재편했다. 이후 1년 10개월 동안 더 빨라진 업무 속도와 여러 화면을 오가는 환경 때문에 오래전부터 대수롭지 않게 넘겨왔던 습관들이 더 두드러지게 나타났다. 그는 절차 중간에 길을 잃고, 티켓 처리를 반쯤 끝낸 채로 남겨두고, 일상적인 후속 조치를 잊어버리고, 코칭 세션 중에 안절부절못하며 자세를 바꾸고, 자기 차례가 되기 전에 동료들의 대화에 끼어들었다. 경력, 고객을 대하는 따뜻함, 지지적인 동료들 덕분에 그럭저럭 버틸 수 있었기에 장애 정도는 경미한 수준이었지만, 업무 평가에서 업무 완수의 일관성 부족과 피할 수 있었던 실수들이 지적되기 시작했다. 직장 웰니스 세미나에서 성인 ADHD 패턴에 대한 설명을 듣고 불편할 정도로 낯익다고 느낀 후, 데니스는 1차 진료의에게 정신건강의학과 의뢰를 요청했다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 저는 스미스 선생님입니다. 오늘 어떤 일로 찾아오셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 음, 가장 큰 건 제가 항상 이거 하다가 저거 하다가 계속 옮겨 다니는 느낌이 든다는 거예요. 그냥 가만히 앉아서 아무것도 안 하는 게 잘 안 돼요. 직장에서 새로 바뀐 체제 때문에 그걸 감추거나 그냥 넘어가기가 더 힘들어져서, 병원에 와서 누구랑 이야기해봐야겠다고 생각했어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 저확률: 주의력결핍 과잉행동장애 (부주의 우세형) (D002)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 항상 움직이거나 바빠야 할 것 같은 이 느낌이 어렸을 때부터 있었던 건지, 아니면 성인이 되고 나서 최근에 시작된 건지 말씀해 주시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 아니요, 새로운 게 아니에요. 돌이켜보면 어렸을 때도 있었어요. 초등학교 때 선생님들이 제가 똑똑한데 좀 덤벙댄다고, 순서 안 지키고 말한다거나 과제에 집중하려면 계속 상기시켜줘야 한다고 하셨어요. 그게 지금이랑 연결된다는 걸 최근에야 제대로 깨달은 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 지금 일상생활에서도 신체적으로 안절부절못하거나, 가만히 있지 못하거나, 다른 사람 말을 끊거나 깊이 생각하지 않고 빠르게 결정을 내리는 것처럼 충동적으로 행동하는 걸 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 네, 그런 걸 느껴요. 교육 영상이나 긴 진료처럼 느린 걸 계속 앉아서 봐야 하면, 뭔가 갇힌 것 같은 느낌이 들기 시작해요. 일어나고 싶고, 몸을 좀 펴고 싶고, 자세를 바꾸고 싶고, 아니면 손으로 뭔가라도 하고 싶어져요. 크게 티가 나진 않는데, 분명히 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 안절부절못하는 느낌이 없을 때도, 세부적인 걸 놓치거나, 뭔가를 잊어버리거나, 업무를 정리하거나 집중하는 데 어려움을 겪으시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 네, 그래요. 주로 긴 회의를 할 때나 직장에서 새 업무 절차를 읽으려고 할 때 그래요. 처음엔 괜찮게 시작하는데, 몇 분 지나면 제 눈은 계속 페이지를 훑고 있었는데도, 아니면 앉아서 듣고는 있었는데도 실제로는 무슨 말인지 제대로 받아들이지 못했다는 걸 깨달아요. 그럼 다시 돌아가서 따라잡으려고 해야 해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
+배경 서술: 데니스가 근무하던 콜센터는 그의 업무를 익숙했던 전화 기반 고객 응대에서 실시간 채팅, CRM 문서 작업, 여러 디지털 플랫폼에 걸친 신속한 에스컬레이션 처리를 함께 담당하는 혼합형 직무로 재편했다. 이후 1년 10개월 동안 더 빨라진 업무 속도와 여러 화면을 오가는 환경 때문에 오래전부터 대수롭지 않게 넘겨왔던 습관들이 더 두드러지게 나타났다. 그는 절차 중간에 길을 잃고, 티켓 처리를 반쯤 끝낸 채로 남겨두고, 일상적인 후속 조치를 잊어버리고, 코칭 세션 중에 안절부절못하며 자세를 바꾸고, 자기 차례가 되기 전에 동료들의 대화에 끼어들었다. 경력, 고객을 대하는 따뜻함, 지지적인 동료들 덕분에 그럭저럭 버틸 수 있었기에 장애 정도는 경미한 수준이었지만, 업무 평가에서 업무 완수의 일관성 부족과 피할 수 있었던 실수들이 지적되기 시작했다. 직장 웰니스 세미나에서 성인 ADHD 패턴에 대한 설명을 듣고 불편할 정도로 낯익다고 느낀 후, 데니스는 1차 진료의에게 정신건강의학과 의뢰를 요청했다.
+표집된 증상 목록:
+  - S001 세부사항 부주의 실수: 세부적인 것에 주의를 기울이지 못하거나 부주의한 실수를 자주 한다.
+  - S002 지속적 주의 유지 곤란: 과제나 놀이 활동에서 주의를 지속하는 데 자주 어려움을 겪는다.
+  - S004 지시 이행 곤란: 지시를 끝까지 따르지 못하고 학업, 집안일, 직장 업무를 제대로 마치지 못하는 경우가 잦다.
+  - S008 산만함: 외부 자극에 의해 쉽게 주의가 분산된다(청소년 후기 및 성인의 경우 관련 없는 생각도 포함될 수 있다).
+  - S009 일상 활동 망각: 일상 활동에서 자주 잊어버린다(예: 집안일, 심부름, 성인의 경우 전화 회신, 청구서 납부, 약속 지키기 등).
+  - S010 손발 꼼지락거림: 손발을 가만두지 못하고 두드리거나 자리에서 꼼지락거리는 경우가 잦다.
+  - S012 안절부절못함: 부적절한 상황에서 자주 뛰어다니거나 기어오른다(청소년/성인의 경우 안절부절못하는 느낌으로 제한될 수 있다).
+  - S013 조용한 활동 곤란: 여가 활동을 조용히 하지 못하는 경우가 잦다.
+  - S014 끊임없는 활동성: 마치 '모터가 달린 것처럼' 끊임없이 활동한다.
+  - S017 차례 기다리기 곤란: 차례를 기다리는 데 자주 어려움을 겪는다.
+  - S018 끼어들기/방해: 다른 사람의 대화나 활동에 자주 끼어들거나 방해한다(예: 대화, 게임, 활동에 불쑥 끼어듦).</t>
+        </is>
+      </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 주의력결핍 과잉행동장애 (복합형) (D001, ICD: F90.2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: inattention (관계=must_include, 요구개수=5, 충족개수=3, 커버리지=0.6)
-  확인된 근거: 세부사항 부주의 실수: 세부적인 것에 주의를 기울이지 못하거나 부주의한 실수를 자주 한다.; 지속적 주의 유지 곤란: 과제나 놀이 활동에서 주의를 지속하는 데 자주 어려움을 겪는다.; 지시 이행 곤란: 지시를 끝까지 따르지 못하고 학업, 집안일, 직장 업무를 제대로 마치지 못하는 경우가 잦다.
-  누락: 경청 곤란: 직접 말을 걸어도 듣지 않는 것처럼 보이는 경우가 잦다.; 조직화 곤란: 과제와 활동을 체계적으로 조직하는 데 자주 어려움을 겪는다.; 지속적 정신적 노력 회피: 지속적인 정신적 노력을 요하는 과제를 자주 피하거나 싫어하거나 꺼린다.; 물건 분실: 과제나 활동에 필요한 물건을 자주 잃어버린다.; 산만함: 외부 자극에 의해 쉽게 주의가 분산된다(청소년 후기 및 성인의 경우 관련 없는 생각도 포함될 수 있다).; 일상 활동 망각: 일상 활동에서 자주 잊어버린다(예: 집안일, 심부름, 성인의 경우 전화 회신, 청구서 납부, 약속 지키기 등).</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: hyperactivity_impulsivity (관계=must_include, 요구개수=5, 충족개수=3, 커버리지=0.6)
-  확인된 근거: 안절부절못함: 부적절한 상황에서 자주 뛰어다니거나 기어오른다(청소년/성인의 경우 안절부절못하는 느낌으로 제한될 수 있다).; 끊임없는 활동성: 마치 '모터가 달린 것처럼' 끊임없이 활동한다.; 과도한 말하기: 지나치게 말을 많이 하는 경우가 잦다.
-  누락: 손발 꼼지락거림: 손발을 가만두지 못하고 두드리거나 자리에서 꼼지락거리는 경우가 잦다.; 자리 이탈: 가만히 앉아 있어야 하는 상황에서 자주 자리를 떠난다.; 조용한 활동 곤란: 여가 활동을 조용히 하지 못하는 경우가 잦다.; 성급한 대답: 질문이 끝나기도 전에 불쑥 대답해버리는 경우가 잦다.; 차례 기다리기 곤란: 차례를 기다리는 데 자주 어려움을 겪는다.; 끼어들기/방해: 다른 사람의 대화나 활동에 자주 끼어들거나 방해한다(예: 대화, 게임, 활동에 불쑥 끼어듦).</t>
+          <t>의사의 최종 진단: 주의력결핍 과잉행동장애 (복합형) (D001, ICD: F90.2)
+지속 기간 요건: 있음
+기능적 손상 요건: 있음
+추가 요건: 있음
+체크리스트 그룹: inattention (관계=must_include, 요구개수=5, 충족개수=3, 커버리지=0.6)
+확인된 근거:
+  - 세부사항 부주의 실수: 세부적인 것에 주의를 기울이지 못하거나 부주의한 실수를 자주 한다.
+  - 지속적 주의 유지 곤란: 과제나 놀이 활동에서 주의를 지속하는 데 자주 어려움을 겪는다.
+  - 지시 이행 곤란: 지시를 끝까지 따르지 못하고 학업, 집안일, 직장 업무를 제대로 마치지 못하는 경우가 잦다.
+체크리스트 그룹: hyperactivity_impulsivity (관계=must_include, 요구개수=5, 충족개수=3, 커버리지=0.6)
+확인된 근거:
+  - 안절부절못함: 부적절한 상황에서 자주 뛰어다니거나 기어오른다(청소년/성인의 경우 안절부절못하는 느낌으로 제한될 수 있다).
+  - 끊임없는 활동성: 마치 '모터가 달린 것처럼' 끊임없이 활동한다.
+  - 과도한 말하기: 지나치게 말을 많이 하는 경우가 잦다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A28:B28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D001_S005_P002__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D001_S005_P002__claude-sonnet-5_kor.xlsx
@@ -649,6 +649,11 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -698,11 +703,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A28:B28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D001_S005_P002__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D001_S005_P002__claude-sonnet-5_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.7708</v>
+        <v>0.7083</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +483,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.9375</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.5833</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.75</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
